--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2016_T3_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2016_T3_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>93</t>
+    <t>89</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,34 +57,34 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.108</t>
-  </si>
-  <si>
-    <t>(0.032)</t>
-  </si>
-  <si>
-    <t>0.290</t>
-  </si>
-  <si>
-    <t>(0.047)</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>(0.018)</t>
-  </si>
-  <si>
-    <t>0.204</t>
-  </si>
-  <si>
-    <t>(0.079)</t>
-  </si>
-  <si>
-    <t>0.527</t>
-  </si>
-  <si>
-    <t>(0.105)</t>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>(0.034)</t>
+  </si>
+  <si>
+    <t>0.303</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>0.034</t>
+  </si>
+  <si>
+    <t>(0.019)</t>
+  </si>
+  <si>
+    <t>0.213</t>
+  </si>
+  <si>
+    <t>(0.082)</t>
+  </si>
+  <si>
+    <t>0.551</t>
+  </si>
+  <si>
+    <t>(0.110)</t>
   </si>
   <si>
     <t>21</t>
@@ -120,7 +120,7 @@
     <t>(0.469)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -132,19 +132,19 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.083</t>
-  </si>
-  <si>
-    <t>0.472***</t>
-  </si>
-  <si>
-    <t>0.158***</t>
-  </si>
-  <si>
-    <t>0.224</t>
-  </si>
-  <si>
-    <t>1.759***</t>
+    <t>0.078</t>
+  </si>
+  <si>
+    <t>0.459***</t>
+  </si>
+  <si>
+    <t>0.157***</t>
+  </si>
+  <si>
+    <t>0.215</t>
+  </si>
+  <si>
+    <t>1.735***</t>
   </si>
 </sst>
 </file>
